--- a/product_selector_out/STM32U0 series - diff.xlsx
+++ b/product_selector_out/STM32U0 series - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$160</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E115"/>
+  <dimension ref="A1:E160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1911</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="18">
@@ -903,17 +903,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -930,17 +930,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -957,17 +957,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2 (workbook and API agree)</t>
+          <t>7 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -984,18 +984,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1007,25 +1011,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32U073MB</t>
+          <t>STM32U073R8</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1035,7 +1043,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1043,63 +1051,55 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32U073MB</t>
+          <t>STM32U073R8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32U073MB</t>
+          <t>STM32U073R8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1111,18 +1111,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1134,52 +1138,56 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32U073M8</t>
+          <t>STM32U073MB</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32U073M8</t>
+          <t>STM32U073MB</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1197,16 +1205,16 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32U073M8</t>
+          <t>STM32U073MB</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1216,7 +1224,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2 (workbook and API agree)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1224,50 +1232,54 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32U073M8</t>
+          <t>STM32U073MB</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32U073M8</t>
+          <t>STM32U073MB</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -1279,180 +1291,192 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32U073RB</t>
+          <t>STM32U073MB</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32U073RB</t>
+          <t>STM32U073M8</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32U073RB</t>
+          <t>STM32U073M8</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2 (workbook and API agree)</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32U073RB</t>
+          <t>STM32U073M8</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32U073RB</t>
+          <t>STM32U073M8</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32U031K8</t>
+          <t>STM32U073M8</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32U031K8</t>
+          <t>STM32U073M8</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32U031F8</t>
+          <t>STM32U073M8</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1475,7 +1499,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32U031F8</t>
+          <t>STM32U073M8</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1498,156 +1522,180 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32U083HC</t>
+          <t>STM32U073RB</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32U083CC</t>
+          <t>STM32U073RB</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32U083CC</t>
+          <t>STM32U073RB</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32U031K4</t>
+          <t>STM32U073RB</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32U031K4</t>
+          <t>STM32U073RB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32U031K6</t>
+          <t>STM32U073RB</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32U031K6</t>
+          <t>STM32U073RB</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -1659,88 +1707,76 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32U073CB</t>
+          <t>STM32U073RB</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32U073CB</t>
+          <t>STM32U031K8</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32U073CB</t>
+          <t>STM32U031K8</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32U073CB</t>
+          <t>STM32U031F8</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1763,7 +1799,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32U073CB</t>
+          <t>STM32U031F8</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1786,88 +1822,76 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32U073C8</t>
+          <t>STM32U083HC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32U073C8</t>
+          <t>STM32U083CC</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32U073C8</t>
+          <t>STM32U083CC</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32U073C8</t>
+          <t>STM32U031K4</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1890,7 +1914,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32U073C8</t>
+          <t>STM32U031K4</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1913,7 +1937,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32U083MC</t>
+          <t>STM32U031K6</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1936,7 +1960,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32U083MC</t>
+          <t>STM32U031K6</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1959,99 +1983,115 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32U083RC</t>
+          <t>STM32U073CB</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32U083RC</t>
+          <t>STM32U073CB</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32U083KC</t>
+          <t>STM32U073CB</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32U083KC</t>
+          <t>STM32U073CB</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32U073KC</t>
+          <t>STM32U073CB</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2069,16 +2109,16 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32U073KC</t>
+          <t>STM32U073CB</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2088,7 +2128,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2096,54 +2136,50 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32U073KC</t>
+          <t>STM32U073CB</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>2 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32U073KC</t>
+          <t>STM32U073CB</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -2155,130 +2191,142 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32U073KC</t>
+          <t>STM32U073C8</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32U073K8</t>
+          <t>STM32U073C8</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32U073K8</t>
+          <t>STM32U073C8</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32U073K8</t>
+          <t>STM32U073C8</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32U073K8</t>
+          <t>STM32U073C8</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32U073CC</t>
+          <t>STM32U073C8</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2288,7 +2336,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2296,70 +2344,62 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32U073CC</t>
+          <t>STM32U073C8</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32U073CC</t>
+          <t>STM32U073C8</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>2 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32U073CC</t>
+          <t>STM32U083MC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2382,7 +2422,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32U073CC</t>
+          <t>STM32U083MC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2405,99 +2445,87 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32U073RC</t>
+          <t>STM32U083RC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32U073RC</t>
+          <t>STM32U083RC</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32U073RC</t>
+          <t>STM32U083KC</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>2 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E92" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32U073RC</t>
+          <t>STM32U083KC</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -2509,84 +2537,88 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32U073RC</t>
+          <t>STM32U073KC</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32U073MC</t>
+          <t>STM32U073KC</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32U073MC</t>
+          <t>STM32U073KC</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32U073MC</t>
+          <t>STM32U073KC</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2596,7 +2628,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2 (workbook and API agree)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2604,62 +2636,70 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E97" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32U073MC</t>
+          <t>STM32U073KC</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32U073MC</t>
+          <t>STM32U073KC</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E99" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32U031G6</t>
+          <t>STM32U073KC</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2682,161 +2722,165 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32U073KB</t>
+          <t>STM32U073KC</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E101" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32U073KB</t>
+          <t>STM32U073K8</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E102" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32U073KB</t>
+          <t>STM32U073K8</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32U073KB</t>
+          <t>STM32U073K8</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32U073H8</t>
+          <t>STM32U073K8</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E105" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32U073H8</t>
+          <t>STM32U073K8</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E106" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32U073H8</t>
+          <t>STM32U073K8</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2846,7 +2890,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2 (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2854,16 +2898,16 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E107" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32U073H8</t>
+          <t>STM32U073K8</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2886,178 +2930,1349 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32U073HB</t>
+          <t>STM32U073K8</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32U073HB</t>
+          <t>STM32U073CC</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E110" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32U073HB</t>
+          <t>STM32U073CC</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2 (workbook and API agree)</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E111" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32U073HB</t>
+          <t>STM32U073CC</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32U031C6</t>
+          <t>STM32U073CC</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr"/>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32U031C6</t>
+          <t>STM32U073CC</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
+          <t>STM32U073CC</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>STM32U073CC</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>STM32U073CC</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>STM32U073CC</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>STM32U073RC</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>STM32U073RC</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>STM32U073RC</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>STM32U073RC</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>STM32U073RC</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>STM32U073RC</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>STM32U073RC</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>STM32U073RC</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>STM32U073MC</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>STM32U073MC</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>STM32U073MC</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>STM32U073MC</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>STM32U073MC</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>STM32U073MC</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>STM32U073MC</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>STM32U073MC</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>STM32U031G6</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>STM32U073KB</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>STM32U073KB</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>STM32U073KB</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>STM32U073KB</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>STM32U073KB</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>STM32U073KB</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>STM32U073KB</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>STM32U073KB</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>STM32U073H8</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>STM32U073H8</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>STM32U073H8</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E146" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>STM32U073H8</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>STM32U073H8</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>STM32U073H8</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E149" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>STM32U073H8</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>STM32U073HB</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>STM32U073HB</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>STM32U073HB</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E153" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>STM32U073HB</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>STM32U073HB</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>STM32U073HB</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E156" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>STM32U073HB</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>STM32U031C6</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>STM32U031C6</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
           <t>STM32U031G8</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B160" t="inlineStr">
         <is>
           <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr">
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E115" s="3" t="inlineStr">
+      <c r="E160" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E115"/>
+  <autoFilter ref="A18:E160"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32U0 series - diff.xlsx
+++ b/product_selector_out/STM32U0 series - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$122</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E160"/>
+  <dimension ref="A1:E122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1894</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="18">
@@ -984,22 +984,18 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1011,95 +1007,99 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32U073R8</t>
+          <t>STM32U073MB</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2 (workbook and API agree)</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32U073R8</t>
+          <t>STM32U073MB</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32U073R8</t>
+          <t>STM32U073MB</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,18 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1138,29 +1134,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32U073MB</t>
+          <t>STM32U073M8</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1170,7 +1162,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>7 (workbook and API agree)</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1178,108 +1170,104 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32U073MB</t>
+          <t>STM32U073M8</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32U073MB</t>
+          <t>STM32U073M8</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32U073MB</t>
+          <t>STM32U073M8</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32U073MB</t>
+          <t>STM32U073M8</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -1291,30 +1279,34 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32U073MB</t>
+          <t>STM32U073RB</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32U073M8</t>
+          <t>STM32U073RB</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1332,16 +1324,16 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32U073M8</t>
+          <t>STM32U073RB</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1351,7 +1343,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1359,124 +1351,108 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32U073M8</t>
+          <t>STM32U073RB</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>7 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32U073M8</t>
+          <t>STM32U073RB</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32U073M8</t>
+          <t>STM32U031K8</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32U073M8</t>
+          <t>STM32U031K8</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32U073M8</t>
+          <t>STM32U031F8</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1499,7 +1475,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32U073M8</t>
+          <t>STM32U031F8</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1522,180 +1498,156 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32U073RB</t>
+          <t>STM32U083HC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32U073RB</t>
+          <t>STM32U083CC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32U073RB</t>
+          <t>STM32U083CC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>7 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32U073RB</t>
+          <t>STM32U031K4</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32U073RB</t>
+          <t>STM32U031K4</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32U073RB</t>
+          <t>STM32U031K6</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32U073RB</t>
+          <t>STM32U031K6</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -1707,76 +1659,88 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32U073RB</t>
+          <t>STM32U073CB</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32U031K8</t>
+          <t>STM32U073CB</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32U031K8</t>
+          <t>STM32U073CB</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32U031F8</t>
+          <t>STM32U073CB</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1799,7 +1763,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32U031F8</t>
+          <t>STM32U073CB</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1822,76 +1786,88 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32U083HC</t>
+          <t>STM32U073C8</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32U083CC</t>
+          <t>STM32U073C8</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32U083CC</t>
+          <t>STM32U073C8</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32U031K4</t>
+          <t>STM32U073C8</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1914,7 +1890,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32U031K4</t>
+          <t>STM32U073C8</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1937,7 +1913,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32U031K6</t>
+          <t>STM32U083MC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1960,7 +1936,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32U031K6</t>
+          <t>STM32U083MC</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1983,203 +1959,191 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32U073CB</t>
+          <t>STM32U083RC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32U073CB</t>
+          <t>STM32U083RC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32U073CB</t>
+          <t>STM32U083KC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>7 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32U073CB</t>
+          <t>STM32U083KC</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32U073CB</t>
+          <t>STM32U073KC</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32U073CB</t>
+          <t>STM32U073KC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2 (workbook and API agree)</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32U073CB</t>
+          <t>STM32U073KC</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32U073CB</t>
+          <t>STM32U073KC</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -2191,34 +2155,30 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32U073C8</t>
+          <t>STM32U073KC</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32U073C8</t>
+          <t>STM32U073K8</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2236,16 +2196,16 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32U073C8</t>
+          <t>STM32U073K8</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2255,7 +2215,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>7 (workbook and API agree)</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2263,97 +2223,97 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32U073C8</t>
+          <t>STM32U073K8</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32U073C8</t>
+          <t>STM32U073K8</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E84" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32U073C8</t>
+          <t>STM32U073K8</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2 (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32U073C8</t>
+          <t>STM32U073K8</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2376,7 +2336,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32U073C8</t>
+          <t>STM32U073K8</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2399,99 +2359,115 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32U083MC</t>
+          <t>STM32U073CC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32U083MC</t>
+          <t>STM32U073CC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32U083RC</t>
+          <t>STM32U073CC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32U083RC</t>
+          <t>STM32U073CC</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32U083KC</t>
+          <t>STM32U073CC</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2514,7 +2490,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32U083KC</t>
+          <t>STM32U073CC</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2537,7 +2513,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32U073KC</t>
+          <t>STM32U073RC</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2564,7 +2540,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32U073KC</t>
+          <t>STM32U073RC</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2591,7 +2567,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32U073KC</t>
+          <t>STM32U073RC</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2618,396 +2594,384 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32U073KC</t>
+          <t>STM32U073RC</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32U073KC</t>
+          <t>STM32U073RC</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32U073KC</t>
+          <t>STM32U073MC</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2 (workbook and API agree)</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E99" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32U073KC</t>
+          <t>STM32U073MC</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32U073KC</t>
+          <t>STM32U073MC</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E101" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32U073K8</t>
+          <t>STM32U073MC</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32U073K8</t>
+          <t>STM32U073MC</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E103" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32U073K8</t>
+          <t>STM32U031G6</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>7 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E104" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32U073K8</t>
+          <t>STM32U073KB</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E105" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32U073K8</t>
+          <t>STM32U073KB</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E106" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32U073K8</t>
+          <t>STM32U073KB</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32U073K8</t>
+          <t>STM32U073KB</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr"/>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32U073K8</t>
+          <t>STM32U073KB</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32U073CC</t>
+          <t>STM32U073KB</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32U073CC</t>
+          <t>STM32U073KB</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32U073CC</t>
+          <t>STM32U073H8</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3017,7 +2981,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>7 (workbook and API agree)</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3025,1254 +2989,264 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E112" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32U073CC</t>
+          <t>STM32U073H8</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E113" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32U073CC</t>
+          <t>STM32U073H8</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32U073CC</t>
+          <t>STM32U073H8</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E115" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32U073CC</t>
+          <t>STM32U073HB</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2 (workbook and API agree)</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E116" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32U073CC</t>
+          <t>STM32U073HB</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32U073CC</t>
+          <t>STM32U073HB</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32U073RC</t>
+          <t>STM32U073HB</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32U073RC</t>
+          <t>STM32U031C6</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E120" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32U073RC</t>
+          <t>STM32U031C6</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>7 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E121" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32U073RC</t>
+          <t>STM32U031G8</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>STM32U073RC</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E123" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>STM32U073RC</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>2 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E124" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>STM32U073RC</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr">
-        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E125" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>STM32U073RC</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E126" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>STM32U073MC</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>STM32U073MC</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E128" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>STM32U073MC</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>7 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E129" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>STM32U073MC</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>STM32U073MC</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E131" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>STM32U073MC</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>2 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E132" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>STM32U073MC</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr"/>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E133" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>STM32U073MC</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E134" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>STM32U031G6</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E135" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>STM32U073KB</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>STM32U073KB</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E137" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>STM32U073KB</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>7 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E138" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>STM32U073KB</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E139" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>STM32U073KB</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E140" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>STM32U073KB</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E141" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>STM32U073KB</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E142" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>STM32U073KB</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E143" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>STM32U073H8</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>STM32U073H8</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E145" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>STM32U073H8</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>7 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E146" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>STM32U073H8</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>STM32U073H8</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E148" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>STM32U073H8</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>2 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E149" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>STM32U073H8</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E150" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>STM32U073HB</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>STM32U073HB</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E152" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>STM32U073HB</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>7 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E153" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>STM32U073HB</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>STM32U073HB</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E155" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>STM32U073HB</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>2 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E156" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>STM32U073HB</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E157" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>STM32U031C6</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr"/>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E158" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>STM32U031C6</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr"/>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E159" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>STM32U031G8</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr"/>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E160" s="3" t="inlineStr">
+      <c r="E122" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E160"/>
+  <autoFilter ref="A18:E122"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32U0 series - diff.xlsx
+++ b/product_selector_out/STM32U0 series - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$136</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E122"/>
+  <dimension ref="A1:E136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1984</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="6">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1908</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="18">
@@ -1025,27 +1025,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32U073MB</t>
+          <t>STM32U073R8</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1070,9 +1066,9 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1085,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>7 (workbook and API agree)</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1097,9 +1093,9 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1111,18 +1107,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1134,13 +1134,13 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -1152,54 +1152,46 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32U073M8</t>
+          <t>STM32U073MB</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32U073M8</t>
+          <t>STM32U073MB</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1208,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>7 (workbook and API agree)</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1224,9 +1216,9 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1238,18 +1230,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1261,99 +1257,91 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32U073RB</t>
+          <t>STM32U073M8</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32U073RB</t>
+          <t>STM32U073M8</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32U073RB</t>
+          <t>STM32U073M8</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>7 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1365,18 +1353,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1388,59 +1380,67 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32U031K8</t>
+          <t>STM32U073RB</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32U031K8</t>
+          <t>STM32U073RB</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -1452,18 +1452,18 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32U031F8</t>
+          <t>STM32U073RB</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -1475,18 +1475,18 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32U031F8</t>
+          <t>STM32U073RB</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -1498,7 +1498,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32U083HC</t>
+          <t>STM32U031K8</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1521,18 +1521,18 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32U083CC</t>
+          <t>STM32U031K8</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -1544,18 +1544,18 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32U083CC</t>
+          <t>STM32U031F8</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -1567,18 +1567,18 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32U031K4</t>
+          <t>STM32U031F8</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -1590,18 +1590,18 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32U031K4</t>
+          <t>STM32U083HC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -1613,7 +1613,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32U031K6</t>
+          <t>STM32U083CC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1636,7 +1636,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32U031K6</t>
+          <t>STM32U083CC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1659,99 +1659,87 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32U073CB</t>
+          <t>STM32U031K4</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32U073CB</t>
+          <t>STM32U031K4</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32U073CB</t>
+          <t>STM32U031K6</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>7 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32U073CB</t>
+          <t>STM32U031K6</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -1768,25 +1756,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32U073C8</t>
+          <t>STM32U073CB</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1804,16 +1796,16 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32U073C8</t>
+          <t>STM32U073CB</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1823,7 +1815,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1831,54 +1823,50 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32U073C8</t>
+          <t>STM32U073CB</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>7 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32U073C8</t>
+          <t>STM32U073CB</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -1890,18 +1878,18 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32U073C8</t>
+          <t>STM32U073CB</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -1913,87 +1901,99 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32U083MC</t>
+          <t>STM32U073C8</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32U083MC</t>
+          <t>STM32U073C8</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32U083RC</t>
+          <t>STM32U073C8</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32U083RC</t>
+          <t>STM32U073C8</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -2005,18 +2005,18 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32U083KC</t>
+          <t>STM32U073C8</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
@@ -2028,18 +2028,18 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32U083KC</t>
+          <t>STM32U073C8</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -2051,99 +2051,87 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32U073KC</t>
+          <t>STM32U083MC</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32U073KC</t>
+          <t>STM32U083MC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32U073KC</t>
+          <t>STM32U083RC</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>7 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32U073KC</t>
+          <t>STM32U083RC</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -2155,18 +2143,18 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32U073KC</t>
+          <t>STM32U083KC</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
@@ -2178,34 +2166,30 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32U073K8</t>
+          <t>STM32U083KC</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32U073K8</t>
+          <t>STM32U073KC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2223,16 +2207,16 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32U073K8</t>
+          <t>STM32U073KC</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2242,7 +2226,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>7 (workbook and API agree)</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2250,81 +2234,77 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E83" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32U073K8</t>
+          <t>STM32U073KC</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32U073K8</t>
+          <t>STM32U073KC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E85" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32U073K8</t>
+          <t>STM32U073KC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -2336,18 +2316,18 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32U073K8</t>
+          <t>STM32U073KC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -2359,7 +2339,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32U073CC</t>
+          <t>STM32U073K8</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2386,7 +2366,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32U073CC</t>
+          <t>STM32U073K8</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2413,7 +2393,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32U073CC</t>
+          <t>STM32U073K8</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2440,7 +2420,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32U073CC</t>
+          <t>STM32U073K8</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2467,41 +2447,45 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32U073CC</t>
+          <t>STM32U073K8</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32U073CC</t>
+          <t>STM32U073K8</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -2513,61 +2497,53 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32U073RC</t>
+          <t>STM32U073K8</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32U073RC</t>
+          <t>STM32U073K8</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32U073RC</t>
+          <t>STM32U073CC</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2577,7 +2553,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>7 (workbook and API agree)</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2585,154 +2561,154 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E96" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32U073RC</t>
+          <t>STM32U073CC</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32U073RC</t>
+          <t>STM32U073CC</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32U073MC</t>
+          <t>STM32U073CC</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32U073MC</t>
+          <t>STM32U073CC</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E100" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32U073MC</t>
+          <t>STM32U073CC</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>7 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E101" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32U073MC</t>
+          <t>STM32U073CC</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
@@ -2744,53 +2720,61 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32U073MC</t>
+          <t>STM32U073RC</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32U031G6</t>
+          <t>STM32U073RC</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32U073KB</t>
+          <t>STM32U073RC</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2800,7 +2784,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2808,251 +2792,235 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E105" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32U073KB</t>
+          <t>STM32U073RC</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E106" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32U073KB</t>
+          <t>STM32U073RC</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>7 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E107" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32U073KB</t>
+          <t>STM32U073RC</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E108" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32U073KB</t>
+          <t>STM32U073MC</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E109" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32U073KB</t>
+          <t>STM32U073MC</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32U073KB</t>
+          <t>STM32U073MC</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32U073H8</t>
+          <t>STM32U073MC</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32U073H8</t>
+          <t>STM32U073MC</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E113" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32U073H8</t>
+          <t>STM32U073MC</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>7 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E114" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32U073H8</t>
+          <t>STM32U031G6</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3075,7 +3043,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32U073HB</t>
+          <t>STM32U073KB</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3102,7 +3070,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32U073HB</t>
+          <t>STM32U073KB</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3129,7 +3097,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32U073HB</t>
+          <t>STM32U073KB</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3156,64 +3124,72 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32U073HB</t>
+          <t>STM32U073KB</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32U031C6</t>
+          <t>STM32U073KB</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32U031C6</t>
+          <t>STM32U073KB</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
@@ -3225,28 +3201,374 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32U031G8</t>
+          <t>STM32U073KB</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>STM32U073KB</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>STM32U073H8</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>STM32U073H8</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>STM32U073H8</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>STM32U073H8</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E122" s="3" t="inlineStr">
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>STM32U073H8</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>STM32U073HB</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>STM32U073HB</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>STM32U073HB</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>STM32U073HB</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>STM32U073HB</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>STM32U031C6</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>STM32U031C6</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>STM32U031G8</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E122"/>
+  <autoFilter ref="A18:E136"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>